--- a/gex_pivot_levels_2026-09-22.xlsx
+++ b/gex_pivot_levels_2026-09-22.xlsx
@@ -15,12 +15,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All Pivots" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ES'!$A$1:$G$21</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NQ'!$A$1:$G$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'ES'!$A$1:$G$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'NQ'!$A$1:$G$28</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'RTY'!$A$1:$G$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'CL'!$A$1:$G$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'GC'!$A$1:$G$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Pivots'!$A$1:$H$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'All Pivots'!$A$1:$H$65</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -532,7 +532,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>7749.42</v>
+        <v>7747.92</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>765</v>
@@ -561,7 +561,7 @@
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>7770.05</v>
+        <v>7768.55</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>7700</v>
@@ -573,12 +573,12 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>-$4.39M</t>
+          <t>-$5.49M</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>+$13.26M</t>
+          <t>+$16.57M</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -590,7 +590,7 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
-        <v>7799.62</v>
+        <v>7798.12</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>770</v>
@@ -623,7 +623,7 @@
     </row>
     <row r="5">
       <c r="A5" s="6" t="n">
-        <v>7805.05</v>
+        <v>7803.55</v>
       </c>
       <c r="B5" s="6" t="n">
         <v>7735</v>
@@ -635,12 +635,12 @@
       </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>-$10.73M</t>
+          <t>-$13.30M</t>
         </is>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>+$21.78M</t>
+          <t>+$26.98M</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
@@ -656,7 +656,7 @@
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7809.65</v>
+        <v>7808.15</v>
       </c>
       <c r="B6" s="2" t="n">
         <v>771</v>
@@ -689,7 +689,7 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>7819.69</v>
+        <v>7818.19</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>772</v>
@@ -722,7 +722,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>7820.05</v>
+        <v>7818.55</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>7750</v>
@@ -734,12 +734,12 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>+$2.82M</t>
+          <t>+$3.35M</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>+$45.26M</t>
+          <t>+$53.81M</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -751,7 +751,7 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7839.77</v>
+        <v>7838.27</v>
       </c>
       <c r="B9" s="2" t="n">
         <v>774</v>
@@ -784,7 +784,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>7845.05</v>
+        <v>7843.55</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>7775</v>
@@ -813,7 +813,7 @@
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
-        <v>7849.81</v>
+        <v>7848.31</v>
       </c>
       <c r="B11" s="6" t="n">
         <v>775</v>
@@ -846,7 +846,7 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7855.05</v>
+        <v>7853.55</v>
       </c>
       <c r="B12" s="2" t="n">
         <v>7785</v>
@@ -858,12 +858,12 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>+$23.57M</t>
+          <t>+$21.44M</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>+$27.15M</t>
+          <t>+$24.71M</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -879,7 +879,7 @@
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>7865.05</v>
+        <v>7863.55</v>
       </c>
       <c r="B13" s="2" t="n">
         <v>7795</v>
@@ -891,12 +891,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>+$10.65M</t>
+          <t>+$8.92M</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>+$11.39M</t>
+          <t>+$9.53M</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -912,7 +912,7 @@
     </row>
     <row r="14">
       <c r="A14" s="6" t="n">
-        <v>7870.05</v>
+        <v>7868.55</v>
       </c>
       <c r="B14" s="6" t="n">
         <v>7800</v>
@@ -924,12 +924,12 @@
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>+$25.52M</t>
+          <t>+$20.28M</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>+$35.97M</t>
+          <t>+$28.59M</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -945,7 +945,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>7875.05</v>
+        <v>7873.55</v>
       </c>
       <c r="B15" s="2" t="n">
         <v>7805</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>+$11.51M</t>
+          <t>+$9.01M</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>+$11.88M</t>
+          <t>+$9.30M</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -978,7 +978,7 @@
     </row>
     <row r="16">
       <c r="A16" s="6" t="n">
-        <v>7880.05</v>
+        <v>7878.55</v>
       </c>
       <c r="B16" s="6" t="n">
         <v>7810</v>
@@ -990,12 +990,12 @@
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>+$24.07M</t>
+          <t>+$18.15M</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>+$24.23M</t>
+          <t>+$18.27M</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>7890.05</v>
+        <v>7898.55</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>7820</v>
+        <v>7830</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
@@ -1023,155 +1023,118 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>+$6.50M</t>
+          <t>+$9.21M</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>+$6.85M</t>
+          <t>+$9.29M</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>7903.55</v>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>7835</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>+$2.91M</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>+$3.08M</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G17" s="3" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="n">
-        <v>7900.05</v>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>7830</v>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="6" t="n">
+        <v>7913.55</v>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>7845</v>
+      </c>
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
-        <is>
-          <t>+$13.05M</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>+$13.16M</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
+        <is>
+          <t>+$12.65M</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>+$12.78M</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G19" s="7" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="n">
-        <v>7905.05</v>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>7835</v>
-      </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>+$4.16M</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>+$4.40M</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
     <row r="20">
-      <c r="A20" s="6" t="n">
-        <v>7915.05</v>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>7845</v>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>+$17.39M</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>+$17.58M</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="n">
-        <v>7980.31</v>
-      </c>
-      <c r="B21" s="2" t="n">
+      <c r="A20" s="2" t="n">
+        <v>7978.81</v>
+      </c>
+      <c r="B20" s="2" t="n">
         <v>788</v>
       </c>
-      <c r="C21" s="3" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="D21" s="4" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>+$4.50M</t>
         </is>
       </c>
-      <c r="E21" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>+$4.50M</t>
         </is>
       </c>
-      <c r="F21" s="3" t="inlineStr">
+      <c r="F20" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G21" s="3" t="inlineStr"/>
+      <c r="G20" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G21"/>
+  <autoFilter ref="A1:G20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1183,7 +1146,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1234,24 +1197,24 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>30080.33</v>
+        <v>30403.46</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>+$858.58K</t>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>-$11.74M</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>+$1.51M</t>
+          <t>+$21.57M</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
@@ -1262,157 +1225,145 @@
       <c r="G2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="n">
-        <v>30203.66</v>
-      </c>
-      <c r="B3" s="6" t="n">
-        <v>725</v>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
+      <c r="A3" s="2" t="n">
+        <v>30567.9</v>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>734</v>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>+$2.78M</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>+$2.88M</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G3" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>-$18.02M</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>+$24.83M</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>30285.88</v>
+        <v>30609.01</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>+$1.21M</t>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>-$15.12M</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>+$1.22M</t>
+          <t>+$35.66M</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n">
-        <v>30491.43</v>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>732</v>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="D5" s="8" t="inlineStr">
-        <is>
-          <t>+$7.76M</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr">
-        <is>
-          <t>+$7.76M</t>
-        </is>
-      </c>
-      <c r="F5" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G5" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="n">
+        <v>30642.65</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>30250</v>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>-$70.11K</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>+$295.68K</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>30573.65</v>
+        <v>30667.65</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>734</v>
+        <v>30275</v>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>+$1.66M</t>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>-$26.82K</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>+$1.66M</t>
+          <t>+$234.71K</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>30648.4</v>
+        <v>30692.65</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>30250</v>
+        <v>30300</v>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>-$70.11K</t>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>+$95.10K</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>+$295.68K</t>
+          <t>+$307.26K</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -1424,24 +1375,24 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>30655.88</v>
+        <v>30732.35</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>+$4.57M</t>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>-$3.75M</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>+$4.58M</t>
+          <t>+$72.83M</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
@@ -1453,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>30673.4</v>
+        <v>30742.65</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>30275</v>
+        <v>30350</v>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
@@ -1465,12 +1416,12 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>-$26.82K</t>
+          <t>-$11.89K</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>+$234.71K</t>
+          <t>+$202.10K</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -1482,10 +1433,10 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>30698.4</v>
+        <v>30772.65</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>30300</v>
+        <v>30380</v>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
@@ -1494,12 +1445,12 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>+$95.10K</t>
+          <t>+$106.69K</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>+$307.26K</t>
+          <t>+$200.57K</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
@@ -1510,87 +1461,91 @@
       <c r="G10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="n">
-        <v>30738.1</v>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>738</v>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
+      <c r="A11" s="2" t="n">
+        <v>30773.46</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>739</v>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D11" s="8" t="inlineStr">
-        <is>
-          <t>+$5.19M</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>+$5.19M</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>+$14.32M</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>+$54.09M</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="n">
+        <v>30792.65</v>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>30400</v>
+      </c>
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="D12" s="8" t="inlineStr">
+        <is>
+          <t>+$546.24K</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>+$853.51K</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Both</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G12" s="7" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>30748.4</v>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>30350</v>
-      </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>-$11.89K</t>
-        </is>
-      </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>+$202.10K</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>30778.4</v>
+        <v>30814.57</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>30380</v>
+        <v>740</v>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>NDX</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>+$106.69K</t>
+          <t>+$6.44M</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>+$200.57K</t>
+          <t>+$64.89M</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1602,247 +1557,247 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>30779.21</v>
+        <v>30842.65</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>739</v>
+        <v>30450</v>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>NDX</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>+$1.61M</t>
+          <t>+$141.44K</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>+$1.61M</t>
+          <t>+$424.31K</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>30867.65</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>30475</v>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>+$53.65K</t>
+        </is>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>+$356.03K</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="n">
-        <v>30798.4</v>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>30400</v>
-      </c>
-      <c r="C15" s="7" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>30892.65</v>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>30500</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D15" s="8" t="inlineStr">
-        <is>
-          <t>+$546.24K</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>+$853.51K</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="n">
-        <v>30820.32</v>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>740</v>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="inlineStr">
-        <is>
-          <t>+$7.53M</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>+$7.53M</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>+$209.72K</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>+$609.65K</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>30848.4</v>
+        <v>30896.79</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>30450</v>
+        <v>742</v>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>-$2.23M</t>
+        </is>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>+$39.79M</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="n">
+        <v>30942.65</v>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>30550</v>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>+$141.44K</t>
-        </is>
-      </c>
-      <c r="E17" s="3" t="inlineStr">
-        <is>
-          <t>+$424.31K</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="n">
-        <v>30873.4</v>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>30475</v>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr">
-        <is>
-          <t>+$53.65K</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>+$356.03K</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>+$317.02K</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>+$375.54K</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>30898.4</v>
+        <v>31020.12</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>30500</v>
+        <v>745</v>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>+$28.68M</t>
+        </is>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>+$31.71M</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>31067.65</v>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>30675</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>+$209.72K</t>
-        </is>
-      </c>
-      <c r="E19" s="3" t="inlineStr">
-        <is>
-          <t>+$609.65K</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="n">
-        <v>30948.4</v>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>30550</v>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="inlineStr">
-        <is>
-          <t>+$317.02K</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>+$375.54K</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>+$58.53K</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>+$58.53K</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>31073.4</v>
+        <v>31102.34</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>30675</v>
+        <v>747</v>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>NDX</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>+$58.53K</t>
+          <t>+$9.84M</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>+$58.53K</t>
+          <t>+$10.10M</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -1858,7 +1813,7 @@
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
-        <v>31123.4</v>
+        <v>31117.65</v>
       </c>
       <c r="B22" s="6" t="n">
         <v>30725</v>
@@ -1891,7 +1846,7 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>31148.4</v>
+        <v>31142.65</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>30750</v>
@@ -1923,74 +1878,70 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n">
-        <v>31190.31</v>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>749</v>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="A24" s="6" t="n">
+        <v>31143.45</v>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>748</v>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D24" s="4" t="inlineStr">
-        <is>
-          <t>+$148.44K</t>
-        </is>
-      </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>+$148.44K</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>+$48.73M</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>+$48.99M</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="n">
-        <v>31231.43</v>
-      </c>
-      <c r="B25" s="6" t="n">
+      <c r="A25" s="2" t="n">
+        <v>31225.68</v>
+      </c>
+      <c r="B25" s="2" t="n">
         <v>750</v>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C25" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>+$1.97M</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>+$1.97M</t>
-        </is>
-      </c>
-      <c r="F25" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G25" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>+$15.34M</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>+$15.75M</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>31248.4</v>
+        <v>31242.65</v>
       </c>
       <c r="B26" s="2" t="n">
         <v>30850</v>
@@ -2019,7 +1970,7 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="n">
-        <v>31298.4</v>
+        <v>31292.65</v>
       </c>
       <c r="B27" s="6" t="n">
         <v>30900</v>
@@ -2052,101 +2003,35 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>31313.65</v>
+        <v>31392.65</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>752</v>
+        <v>31000</v>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>NDX</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>+$18.79K</t>
+          <t>+$101.51K</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>+$18.79K</t>
+          <t>+$101.51K</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="n">
-        <v>31398.4</v>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>31000</v>
-      </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>+$101.51K</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>+$101.51K</t>
-        </is>
-      </c>
-      <c r="F29" s="3" t="inlineStr">
-        <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="G29" s="3" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="n">
-        <v>31519.2</v>
-      </c>
-      <c r="B30" s="6" t="n">
-        <v>757</v>
-      </c>
-      <c r="C30" s="7" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>+$1.99M</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>+$1.99M</t>
-        </is>
-      </c>
-      <c r="F30" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="G30" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="G28" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G30"/>
+  <autoFilter ref="A1:G28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2370,7 +2255,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>87.76000000000001</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>140</v>
@@ -2399,7 +2284,7 @@
     </row>
     <row r="3">
       <c r="A3" s="6" t="n">
-        <v>90.90000000000001</v>
+        <v>90.98999999999999</v>
       </c>
       <c r="B3" s="6" t="n">
         <v>145</v>
@@ -2432,7 +2317,7 @@
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>92.78</v>
+        <v>92.87</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>148</v>
@@ -2461,7 +2346,7 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>93.41</v>
+        <v>93.5</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>149</v>
@@ -2494,7 +2379,7 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>94.03</v>
+        <v>94.12</v>
       </c>
       <c r="B6" s="6" t="n">
         <v>150</v>
@@ -2527,7 +2412,7 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>96.54000000000001</v>
+        <v>96.63</v>
       </c>
       <c r="B7" s="2" t="n">
         <v>154</v>
@@ -2618,7 +2503,7 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>4178.33</v>
+        <v>4173.66</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>90</v>
@@ -2647,7 +2532,7 @@
     </row>
     <row r="3">
       <c r="A3" s="6" t="n">
-        <v>4317.61</v>
+        <v>4312.79</v>
       </c>
       <c r="B3" s="6" t="n">
         <v>93</v>
@@ -2680,7 +2565,7 @@
     </row>
     <row r="4">
       <c r="A4" s="6" t="n">
-        <v>4346.8</v>
+        <v>4341.95</v>
       </c>
       <c r="B4" s="6" t="n">
         <v>395</v>
@@ -2692,12 +2577,12 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>-$2.84M</t>
+          <t>-$4.07M</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>+$3.19M</t>
+          <t>+$4.94M</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
@@ -2713,10 +2598,10 @@
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>4401.83</v>
+        <v>4374.92</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
@@ -2725,12 +2610,12 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>-$243.26K</t>
+          <t>-$357.61K</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>+$1.20M</t>
+          <t>+$2.79M</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -2742,10 +2627,10 @@
     </row>
     <row r="6">
       <c r="A6" s="6" t="n">
-        <v>4434.84</v>
+        <v>4396.91</v>
       </c>
       <c r="B6" s="6" t="n">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
@@ -2754,12 +2639,12 @@
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>+$944.36K</t>
+          <t>+$3.44M</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>+$1.08M</t>
+          <t>+$5.02M</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
@@ -2775,7 +2660,7 @@
     </row>
     <row r="7">
       <c r="A7" s="6" t="n">
-        <v>4503.31</v>
+        <v>4498.28</v>
       </c>
       <c r="B7" s="6" t="n">
         <v>97</v>
@@ -2808,7 +2693,7 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>4596.17</v>
+        <v>4591.03</v>
       </c>
       <c r="B8" s="2" t="n">
         <v>99</v>
@@ -2841,7 +2726,7 @@
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
-        <v>4642.59</v>
+        <v>4637.4</v>
       </c>
       <c r="B9" s="6" t="n">
         <v>100</v>
@@ -2874,7 +2759,7 @@
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>4735.44</v>
+        <v>4730.15</v>
       </c>
       <c r="B10" s="2" t="n">
         <v>102</v>
@@ -2914,7 +2799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H68"/>
+  <dimension ref="A1:H65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2970,68 +2855,64 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="n">
-        <v>7819.69</v>
-      </c>
-      <c r="C2" s="6" t="n">
-        <v>772</v>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>+$39.91M</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>+$46.29M</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="n">
+        <v>30732.35</v>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>738</v>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>-$3.75M</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>+$72.83M</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>7820.05</v>
+        <v>30814.57</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>7750</v>
+        <v>740</v>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>SPX</t>
+          <t>QQQ</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>+$2.82M</t>
+          <t>+$6.44M</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>+$45.26M</t>
+          <t>+$64.89M</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -3042,38 +2923,38 @@
       <c r="H3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="7" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>7870.05</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>7800</v>
-      </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>+$25.52M</t>
-        </is>
-      </c>
-      <c r="F4" s="7" t="inlineStr">
-        <is>
-          <t>+$35.97M</t>
-        </is>
-      </c>
-      <c r="G4" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>30773.46</v>
+      </c>
+      <c r="C4" s="2" t="n">
+        <v>739</v>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>+$14.32M</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>+$54.09M</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -3086,10 +2967,10 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>7845.05</v>
+        <v>7818.55</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>7775</v>
+        <v>7750</v>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
@@ -3098,12 +2979,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>+$13.35M</t>
+          <t>+$3.35M</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>+$34.16M</t>
+          <t>+$53.81M</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -3114,38 +2995,38 @@
       <c r="H5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>7855.05</v>
-      </c>
-      <c r="C6" s="2" t="n">
-        <v>7785</v>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="inlineStr">
-        <is>
-          <t>+$23.57M</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
-        <is>
-          <t>+$27.15M</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>31143.45</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>748</v>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>+$48.73M</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>+$48.99M</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -3154,28 +3035,28 @@
     <row r="7">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>2897.28</v>
+        <v>7818.19</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>288</v>
+        <v>772</v>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>+$15.07M</t>
+          <t>+$39.91M</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>+$24.89M</t>
+          <t>+$46.29M</t>
         </is>
       </c>
       <c r="G7" s="7" t="inlineStr">
@@ -3190,152 +3071,144 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="inlineStr">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>30896.79</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>742</v>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>-$2.23M</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>+$39.79M</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>30609.01</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>735</v>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>-$15.12M</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>+$35.66M</t>
+        </is>
+      </c>
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>7880.05</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>7810</v>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="B10" s="2" t="n">
+        <v>7843.55</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>7775</v>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>+$24.07M</t>
-        </is>
-      </c>
-      <c r="F8" s="7" t="inlineStr">
-        <is>
-          <t>+$24.23M</t>
-        </is>
-      </c>
-      <c r="G8" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
-        <v>7805.05</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>7735</v>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>-$10.73M</t>
-        </is>
-      </c>
-      <c r="F9" s="7" t="inlineStr">
-        <is>
-          <t>+$21.78M</t>
-        </is>
-      </c>
-      <c r="G9" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>7799.62</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>770</v>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>+$16.37M</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>+$18.55M</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>+$13.35M</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>+$34.16M</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>RTY</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>2877.16</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>286</v>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>IWM</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>+$15.23M</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>+$18.53M</t>
-        </is>
-      </c>
-      <c r="G11" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>31020.12</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>745</v>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>+$28.68M</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>+$31.71M</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -3348,10 +3221,10 @@
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>7915.05</v>
+        <v>7868.55</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>7845</v>
+        <v>7800</v>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
@@ -3360,12 +3233,12 @@
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>+$17.39M</t>
+          <t>+$20.28M</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>+$17.58M</t>
+          <t>+$28.59M</t>
         </is>
       </c>
       <c r="G12" s="7" t="inlineStr">
@@ -3386,24 +3259,24 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>7849.81</v>
+        <v>7803.55</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>775</v>
+        <v>7735</v>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>+$15.19M</t>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>-$13.30M</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>+$15.26M</t>
+          <t>+$26.98M</t>
         </is>
       </c>
       <c r="G13" s="7" t="inlineStr">
@@ -3413,115 +3286,119 @@
       </c>
       <c r="H13" s="7" t="inlineStr">
         <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="7" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>2897.28</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>288</v>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E14" s="8" t="inlineStr">
+        <is>
+          <t>+$15.07M</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>+$24.89M</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>30567.9</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>734</v>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>-$18.02M</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>+$24.83M</t>
+        </is>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B14" s="2" t="n">
-        <v>7770.05</v>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>7700</v>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
+      <c r="B16" s="2" t="n">
+        <v>7853.55</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>7785</v>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>-$4.39M</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
-        <is>
-          <t>+$13.26M</t>
-        </is>
-      </c>
-      <c r="G14" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>7900.05</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>7830</v>
-      </c>
-      <c r="D15" s="7" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>+$13.05M</t>
-        </is>
-      </c>
-      <c r="F15" s="7" t="inlineStr">
-        <is>
-          <t>+$13.16M</t>
-        </is>
-      </c>
-      <c r="G15" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="n">
-        <v>4503.31</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>97</v>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E16" s="8" t="inlineStr">
-        <is>
-          <t>+$12.43M</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>+$12.67M</t>
-        </is>
-      </c>
-      <c r="G16" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>+$21.44M</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>+$24.71M</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
@@ -3530,252 +3407,244 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>30403.46</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>730</v>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>-$11.74M</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>+$21.57M</t>
+        </is>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
+        <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n">
-        <v>7875.05</v>
-      </c>
-      <c r="C17" s="2" t="n">
-        <v>7805</v>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="B18" s="6" t="n">
+        <v>7798.12</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>770</v>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>+$16.37M</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>+$18.55M</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="7" t="inlineStr">
+        <is>
+          <t>RTY</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>2877.16</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>286</v>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="E19" s="8" t="inlineStr">
+        <is>
+          <t>+$15.23M</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>+$18.53M</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>7878.55</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>7810</v>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>+$11.51M</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>+$11.88M</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>+$18.15M</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>+$18.27M</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B18" s="2" t="n">
-        <v>7865.05</v>
-      </c>
-      <c r="C18" s="2" t="n">
-        <v>7795</v>
-      </c>
-      <c r="D18" s="3" t="inlineStr">
+      <c r="B21" s="2" t="n">
+        <v>7768.55</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>7700</v>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>SPX</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>+$10.65M</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t>+$11.39M</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>7749.42</v>
-      </c>
-      <c r="C19" s="2" t="n">
-        <v>765</v>
-      </c>
-      <c r="D19" s="3" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>+$6.08M</t>
-        </is>
-      </c>
-      <c r="F19" s="3" t="inlineStr">
-        <is>
-          <t>+$11.38M</t>
-        </is>
-      </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>-$5.49M</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>+$16.57M</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>7839.77</v>
-      </c>
-      <c r="C20" s="2" t="n">
-        <v>774</v>
-      </c>
-      <c r="D20" s="3" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>+$7.77M</t>
-        </is>
-      </c>
-      <c r="F20" s="3" t="inlineStr">
-        <is>
-          <t>+$9.25M</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>4642.59</v>
-      </c>
-      <c r="C21" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>+$8.84M</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>+$9.24M</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="H21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B22" s="6" t="n">
-        <v>30491.43</v>
-      </c>
-      <c r="C22" s="6" t="n">
-        <v>732</v>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="B22" s="2" t="n">
+        <v>31225.68</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>750</v>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>+$7.76M</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>+$7.76M</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>+$15.34M</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>+$15.75M</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>30820.32</v>
+        <v>7848.31</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>740</v>
+        <v>775</v>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>+$7.53M</t>
+          <t>+$15.19M</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>+$7.53M</t>
+          <t>+$15.26M</t>
         </is>
       </c>
       <c r="G23" s="7" t="inlineStr">
@@ -3790,258 +3659,254 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>ES</t>
         </is>
       </c>
-      <c r="B24" s="2" t="n">
-        <v>7809.65</v>
-      </c>
-      <c r="C24" s="2" t="n">
-        <v>771</v>
-      </c>
-      <c r="D24" s="3" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>+$6.63M</t>
-        </is>
-      </c>
-      <c r="F24" s="3" t="inlineStr">
-        <is>
-          <t>+$7.08M</t>
-        </is>
-      </c>
-      <c r="G24" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="B24" s="6" t="n">
+        <v>7913.55</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>7845</v>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>+$12.65M</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>+$12.78M</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>ES</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>7890.05</v>
-      </c>
-      <c r="C25" s="2" t="n">
-        <v>7820</v>
-      </c>
-      <c r="D25" s="3" t="inlineStr">
-        <is>
-          <t>SPX</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>+$6.50M</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="inlineStr">
-        <is>
-          <t>+$6.85M</t>
-        </is>
-      </c>
-      <c r="G25" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>GC</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>4498.28</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>+$12.43M</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>+$12.67M</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>4596.17</v>
+        <v>7747.92</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>99</v>
+        <v>765</v>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>GDX</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>+$5.44M</t>
+          <t>+$6.08M</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>+$5.67M</t>
+          <t>+$11.38M</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>31102.34</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>747</v>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>+$9.84M</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>+$10.10M</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H27" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n">
-        <v>4317.61</v>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>93</v>
-      </c>
-      <c r="D27" s="7" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E27" s="9" t="inlineStr">
-        <is>
-          <t>-$5.48M</t>
-        </is>
-      </c>
-      <c r="F27" s="7" t="inlineStr">
-        <is>
-          <t>+$5.66M</t>
-        </is>
-      </c>
-      <c r="G27" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H27" s="7" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>7863.55</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>7795</v>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>+$8.92M</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>+$9.53M</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>CL</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>90.90000000000001</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>145</v>
-      </c>
-      <c r="D28" s="7" t="inlineStr">
-        <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E28" s="9" t="inlineStr">
-        <is>
-          <t>-$4.58M</t>
-        </is>
-      </c>
-      <c r="F28" s="7" t="inlineStr">
-        <is>
-          <t>+$5.31M</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H28" s="7" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>7873.55</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>7805</v>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>SPX</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>+$9.01M</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>+$9.30M</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
         <is>
           <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="n">
-        <v>30738.1</v>
-      </c>
-      <c r="C29" s="6" t="n">
-        <v>738</v>
-      </c>
-      <c r="D29" s="7" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>+$5.19M</t>
-        </is>
-      </c>
-      <c r="F29" s="7" t="inlineStr">
-        <is>
-          <t>+$5.19M</t>
-        </is>
-      </c>
-      <c r="G29" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H29" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>30655.88</v>
+        <v>7898.55</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>736</v>
+        <v>7830</v>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>+$4.57M</t>
+          <t>+$9.21M</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>+$4.58M</t>
+          <t>+$9.29M</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -4058,10 +3923,10 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>7980.31</v>
+        <v>7838.27</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>788</v>
+        <v>774</v>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
@@ -4070,46 +3935,50 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>+$4.50M</t>
+          <t>+$7.77M</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>+$4.50M</t>
+          <t>+$9.25M</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B32" s="6" t="n">
-        <v>94.03</v>
+        <v>4637.4</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E32" s="9" t="inlineStr">
-        <is>
-          <t>-$3.71M</t>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>+$8.84M</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>+$4.49M</t>
+          <t>+$9.24M</t>
         </is>
       </c>
       <c r="G32" s="7" t="inlineStr">
@@ -4119,7 +3988,7 @@
       </c>
       <c r="H32" s="7" t="inlineStr">
         <is>
-          <t>valley</t>
+          <t>peak</t>
         </is>
       </c>
     </row>
@@ -4130,24 +3999,24 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>7905.05</v>
+        <v>7808.15</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>7835</v>
+        <v>771</v>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>SPX</t>
+          <t>SPY</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>+$4.16M</t>
+          <t>+$6.63M</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>+$4.40M</t>
+          <t>+$7.08M</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -4164,28 +4033,28 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>RTY</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>2887.22</v>
+        <v>4591.03</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>287</v>
+        <v>99</v>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>+$411.91K</t>
+          <t>+$5.44M</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>+$4.23M</t>
+          <t>+$5.67M</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -4206,24 +4075,24 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
-        <v>4346.8</v>
+        <v>4312.79</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>395</v>
+        <v>93</v>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>GDX</t>
         </is>
       </c>
       <c r="E35" s="9" t="inlineStr">
         <is>
-          <t>-$2.84M</t>
+          <t>-$5.48M</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>+$3.19M</t>
+          <t>+$5.66M</t>
         </is>
       </c>
       <c r="G35" s="7" t="inlineStr">
@@ -4238,64 +4107,68 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>GC</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n">
-        <v>4735.44</v>
-      </c>
-      <c r="C36" s="2" t="n">
-        <v>102</v>
-      </c>
-      <c r="D36" s="3" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>+$2.91M</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t>+$2.95M</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr"/>
+      <c r="A36" s="7" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>90.98999999999999</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>145</v>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E36" s="9" t="inlineStr">
+        <is>
+          <t>-$4.58M</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>+$5.31M</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B37" s="6" t="n">
-        <v>30203.66</v>
+        <v>4396.91</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>725</v>
+        <v>400</v>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>GLD</t>
         </is>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
-          <t>+$2.78M</t>
+          <t>+$3.44M</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>+$2.88M</t>
+          <t>+$5.02M</t>
         </is>
       </c>
       <c r="G37" s="7" t="inlineStr">
@@ -4310,102 +4183,102 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="7" t="inlineStr">
         <is>
           <t>GC</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n">
-        <v>4178.33</v>
-      </c>
-      <c r="C38" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>GDX</t>
-        </is>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
-        <is>
-          <t>-$2.00M</t>
-        </is>
-      </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>+$2.70M</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="B38" s="6" t="n">
+        <v>4341.95</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>395</v>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E38" s="9" t="inlineStr">
+        <is>
+          <t>-$4.07M</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>+$4.94M</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>valley</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>7978.81</v>
+      </c>
+      <c r="C39" s="2" t="n">
+        <v>788</v>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>+$4.50M</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>+$4.50M</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="n">
-        <v>31519.2</v>
-      </c>
-      <c r="C39" s="6" t="n">
-        <v>757</v>
-      </c>
-      <c r="D39" s="7" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
-        <is>
-          <t>+$1.99M</t>
-        </is>
-      </c>
-      <c r="F39" s="7" t="inlineStr">
-        <is>
-          <t>+$1.99M</t>
-        </is>
-      </c>
-      <c r="G39" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H39" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="H39" s="3" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="7" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B40" s="6" t="n">
-        <v>31231.43</v>
+        <v>94.12</v>
       </c>
       <c r="C40" s="6" t="n">
-        <v>750</v>
+        <v>150</v>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>+$1.97M</t>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E40" s="9" t="inlineStr">
+        <is>
+          <t>-$3.71M</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>+$1.97M</t>
+          <t>+$4.49M</t>
         </is>
       </c>
       <c r="G40" s="7" t="inlineStr">
@@ -4415,35 +4288,35 @@
       </c>
       <c r="H40" s="7" t="inlineStr">
         <is>
-          <t>peak</t>
+          <t>valley</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>RTY</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>30573.65</v>
+        <v>2887.22</v>
       </c>
       <c r="C41" s="2" t="n">
-        <v>734</v>
+        <v>287</v>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>IWM</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>+$1.66M</t>
+          <t>+$411.91K</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>+$1.66M</t>
+          <t>+$4.23M</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -4460,28 +4333,28 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>30779.21</v>
+        <v>7903.55</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>739</v>
+        <v>7835</v>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>SPX</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>+$1.61M</t>
+          <t>+$2.91M</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>+$1.61M</t>
+          <t>+$3.08M</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -4498,28 +4371,28 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>92.78</v>
+        <v>4730.15</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>148</v>
+        <v>102</v>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>-$1.38M</t>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>+$2.91M</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>+$1.52M</t>
+          <t>+$2.95M</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -4532,28 +4405,28 @@
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B44" s="2" t="n">
-        <v>30080.33</v>
+        <v>4374.92</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>722</v>
+        <v>398</v>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>+$858.58K</t>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>-$357.61K</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>+$1.51M</t>
+          <t>+$2.79M</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -4566,66 +4439,62 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>GC</t>
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>30285.88</v>
+        <v>4173.66</v>
       </c>
       <c r="C45" s="2" t="n">
-        <v>727</v>
+        <v>90</v>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>+$1.21M</t>
+          <t>GDX</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>-$2.00M</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>+$1.22M</t>
+          <t>+$2.70M</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H45" s="3" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B46" s="2" t="n">
-        <v>4401.83</v>
+        <v>92.87</v>
       </c>
       <c r="C46" s="2" t="n">
-        <v>400</v>
+        <v>148</v>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>USO</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
         <is>
-          <t>-$243.26K</t>
+          <t>-$1.38M</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>+$1.20M</t>
+          <t>+$1.52M</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -4638,28 +4507,28 @@
     <row r="47">
       <c r="A47" s="7" t="inlineStr">
         <is>
-          <t>GC</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B47" s="6" t="n">
-        <v>4434.84</v>
+        <v>31117.65</v>
       </c>
       <c r="C47" s="6" t="n">
-        <v>403</v>
+        <v>30725</v>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>GLD</t>
+          <t>NDX</t>
         </is>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>+$944.36K</t>
+          <t>+$874.84K</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>+$1.08M</t>
+          <t>+$880.94K</t>
         </is>
       </c>
       <c r="G47" s="7" t="inlineStr">
@@ -4680,10 +4549,10 @@
         </is>
       </c>
       <c r="B48" s="6" t="n">
-        <v>31123.4</v>
+        <v>30792.65</v>
       </c>
       <c r="C48" s="6" t="n">
-        <v>30725</v>
+        <v>30400</v>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
@@ -4692,12 +4561,12 @@
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>+$874.84K</t>
+          <t>+$546.24K</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>+$880.94K</t>
+          <t>+$853.51K</t>
         </is>
       </c>
       <c r="G48" s="7" t="inlineStr">
@@ -4712,68 +4581,64 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="7" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B49" s="6" t="n">
-        <v>30798.4</v>
-      </c>
-      <c r="C49" s="6" t="n">
-        <v>30400</v>
-      </c>
-      <c r="D49" s="7" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>+$546.24K</t>
-        </is>
-      </c>
-      <c r="F49" s="7" t="inlineStr">
-        <is>
-          <t>+$853.51K</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H49" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>CL</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>96.63</v>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="D49" s="3" t="inlineStr">
+        <is>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>-$553.95K</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>+$829.80K</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>96.54000000000001</v>
+        <v>30892.65</v>
       </c>
       <c r="C50" s="2" t="n">
-        <v>154</v>
+        <v>30500</v>
       </c>
       <c r="D50" s="3" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>-$553.95K</t>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>+$209.72K</t>
         </is>
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>+$829.80K</t>
+          <t>+$609.65K</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -4786,28 +4651,28 @@
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>30898.4</v>
+        <v>87.84999999999999</v>
       </c>
       <c r="C51" s="2" t="n">
-        <v>30500</v>
+        <v>140</v>
       </c>
       <c r="D51" s="3" t="inlineStr">
         <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>+$209.72K</t>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>-$559.87K</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>+$609.65K</t>
+          <t>+$580.51K</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -4820,28 +4685,28 @@
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>87.76000000000001</v>
+        <v>30842.65</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>140</v>
+        <v>30450</v>
       </c>
       <c r="D52" s="3" t="inlineStr">
         <is>
-          <t>USO</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>-$559.87K</t>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>+$141.44K</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>+$580.51K</t>
+          <t>+$424.31K</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -4852,74 +4717,78 @@
       <c r="H52" s="3" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="7" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B53" s="2" t="n">
-        <v>30848.4</v>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>30450</v>
-      </c>
-      <c r="D53" s="3" t="inlineStr">
+      <c r="B53" s="6" t="n">
+        <v>30942.65</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>30550</v>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>+$141.44K</t>
-        </is>
-      </c>
-      <c r="F53" s="3" t="inlineStr">
-        <is>
-          <t>+$424.31K</t>
-        </is>
-      </c>
-      <c r="G53" s="3" t="inlineStr">
-        <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr"/>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>+$317.02K</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>+$375.54K</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="54">
-      <c r="A54" s="7" t="inlineStr">
+      <c r="A54" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B54" s="6" t="n">
-        <v>30948.4</v>
-      </c>
-      <c r="C54" s="6" t="n">
-        <v>30550</v>
-      </c>
-      <c r="D54" s="7" t="inlineStr">
+      <c r="B54" s="2" t="n">
+        <v>30867.65</v>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>30475</v>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E54" s="8" t="inlineStr">
-        <is>
-          <t>+$317.02K</t>
-        </is>
-      </c>
-      <c r="F54" s="7" t="inlineStr">
-        <is>
-          <t>+$375.54K</t>
-        </is>
-      </c>
-      <c r="G54" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H54" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>+$53.65K</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>+$356.03K</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H54" s="3" t="inlineStr">
+        <is>
+          <t>valley</t>
         </is>
       </c>
     </row>
@@ -4930,10 +4799,10 @@
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>30873.4</v>
+        <v>30692.65</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>30475</v>
+        <v>30300</v>
       </c>
       <c r="D55" s="3" t="inlineStr">
         <is>
@@ -4942,168 +4811,164 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>+$53.65K</t>
+          <t>+$95.10K</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>+$356.03K</t>
+          <t>+$307.26K</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H55" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H55" s="3" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>NQ</t>
+          <t>CL</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>30698.4</v>
+        <v>93.5</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>30300</v>
+        <v>149</v>
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>+$95.10K</t>
+          <t>USO</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>-$130.45K</t>
         </is>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>+$307.26K</t>
+          <t>+$296.81K</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H56" s="3" t="inlineStr"/>
+          <t>Net</t>
+        </is>
+      </c>
+      <c r="H56" s="3" t="inlineStr">
+        <is>
+          <t>peak</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>CL</t>
+          <t>NQ</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>93.41</v>
+        <v>30642.65</v>
       </c>
       <c r="C57" s="2" t="n">
-        <v>149</v>
+        <v>30250</v>
       </c>
       <c r="D57" s="3" t="inlineStr">
         <is>
-          <t>USO</t>
+          <t>NDX</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>-$130.45K</t>
+          <t>-$70.11K</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>+$296.81K</t>
+          <t>+$295.68K</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
+          <t>Abs</t>
+        </is>
+      </c>
+      <c r="H57" s="3" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="7" t="inlineStr">
+        <is>
+          <t>NQ</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>31292.65</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>30900</v>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>NDX</t>
+        </is>
+      </c>
+      <c r="E58" s="8" t="inlineStr">
+        <is>
+          <t>+$238.98K</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>+$241.42K</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
         <is>
           <t>peak</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>NQ</t>
         </is>
       </c>
-      <c r="B58" s="2" t="n">
-        <v>30648.4</v>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>30250</v>
-      </c>
-      <c r="D58" s="3" t="inlineStr">
+      <c r="B59" s="2" t="n">
+        <v>30667.65</v>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>30275</v>
+      </c>
+      <c r="D59" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>-$70.11K</t>
-        </is>
-      </c>
-      <c r="F58" s="3" t="inlineStr">
-        <is>
-          <t>+$295.68K</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>-$26.82K</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>+$234.71K</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
         <is>
           <t>Abs</t>
         </is>
       </c>
-      <c r="H58" s="3" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="7" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B59" s="6" t="n">
-        <v>31298.4</v>
-      </c>
-      <c r="C59" s="6" t="n">
-        <v>30900</v>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="inlineStr">
-        <is>
-          <t>+$238.98K</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>+$241.42K</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="inlineStr">
-        <is>
-          <t>Both</t>
-        </is>
-      </c>
-      <c r="H59" s="7" t="inlineStr">
-        <is>
-          <t>peak</t>
-        </is>
-      </c>
+      <c r="H59" s="3" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
@@ -5112,10 +4977,10 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>30673.4</v>
+        <v>30742.65</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>30275</v>
+        <v>30350</v>
       </c>
       <c r="D60" s="3" t="inlineStr">
         <is>
@@ -5124,12 +4989,12 @@
       </c>
       <c r="E60" s="5" t="inlineStr">
         <is>
-          <t>-$26.82K</t>
+          <t>-$11.89K</t>
         </is>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>+$234.71K</t>
+          <t>+$202.10K</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -5146,24 +5011,24 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>30748.4</v>
+        <v>30772.65</v>
       </c>
       <c r="C61" s="2" t="n">
-        <v>30350</v>
+        <v>30380</v>
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
           <t>NDX</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr">
-        <is>
-          <t>-$11.89K</t>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>+$106.69K</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>+$202.10K</t>
+          <t>+$200.57K</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -5180,10 +5045,10 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>30778.4</v>
+        <v>31242.65</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>30380</v>
+        <v>30850</v>
       </c>
       <c r="D62" s="3" t="inlineStr">
         <is>
@@ -5192,12 +5057,12 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>+$106.69K</t>
+          <t>+$155.46K</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>+$200.57K</t>
+          <t>+$155.46K</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -5214,10 +5079,10 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>31248.4</v>
+        <v>31392.65</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>30850</v>
+        <v>31000</v>
       </c>
       <c r="D63" s="3" t="inlineStr">
         <is>
@@ -5226,12 +5091,12 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>+$155.46K</t>
+          <t>+$101.51K</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>+$155.46K</t>
+          <t>+$101.51K</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -5248,24 +5113,24 @@
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>31190.31</v>
+        <v>31142.65</v>
       </c>
       <c r="C64" s="2" t="n">
-        <v>749</v>
+        <v>30750</v>
       </c>
       <c r="D64" s="3" t="inlineStr">
         <is>
-          <t>QQQ</t>
+          <t>NDX</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>+$148.44K</t>
+          <t>+$32.92K</t>
         </is>
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>+$148.44K</t>
+          <t>+$71.33K</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -5286,10 +5151,10 @@
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>31398.4</v>
+        <v>31067.65</v>
       </c>
       <c r="C65" s="2" t="n">
-        <v>31000</v>
+        <v>30675</v>
       </c>
       <c r="D65" s="3" t="inlineStr">
         <is>
@@ -5298,137 +5163,27 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>+$101.51K</t>
+          <t>+$58.53K</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>+$101.51K</t>
+          <t>+$58.53K</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>Abs</t>
-        </is>
-      </c>
-      <c r="H65" s="3" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="n">
-        <v>31148.4</v>
-      </c>
-      <c r="C66" s="2" t="n">
-        <v>30750</v>
-      </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>+$32.92K</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>+$71.33K</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
           <t>Net</t>
         </is>
       </c>
-      <c r="H66" s="3" t="inlineStr">
+      <c r="H65" s="3" t="inlineStr">
         <is>
           <t>valley</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="n">
-        <v>31073.4</v>
-      </c>
-      <c r="C67" s="2" t="n">
-        <v>30675</v>
-      </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>NDX</t>
-        </is>
-      </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>+$58.53K</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="inlineStr">
-        <is>
-          <t>+$58.53K</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H67" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>NQ</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="n">
-        <v>31313.65</v>
-      </c>
-      <c r="C68" s="2" t="n">
-        <v>752</v>
-      </c>
-      <c r="D68" s="3" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>+$18.79K</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="inlineStr">
-        <is>
-          <t>+$18.79K</t>
-        </is>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t>Net</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t>valley</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:H68"/>
+  <autoFilter ref="A1:H65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>